--- a/数据库表结构.xlsx
+++ b/数据库表结构.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="367">
   <si>
     <t>数据库名：lab</t>
   </si>
@@ -682,11 +682,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>状态（使用中</t>
     </r>
     <r>
@@ -703,7 +698,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>已废弃</t>
+      <t>待更换</t>
     </r>
     <r>
       <rPr>
@@ -721,6 +716,12 @@
       </rPr>
       <t>已更换）</t>
     </r>
+  </si>
+  <si>
+    <t>remark</t>
+  </si>
+  <si>
+    <t>组件备注</t>
   </si>
   <si>
     <t>specification</t>
@@ -3626,7 +3627,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F204"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -4706,7 +4707,7 @@
         <v>112</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>113</v>
@@ -4726,7 +4727,7 @@
         <v>114</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>115</v>
@@ -4746,7 +4747,7 @@
         <v>116</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>117</v>
@@ -4763,33 +4764,33 @@
         <v>102</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>27</v>
       </c>
       <c r="F57" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="7" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4797,19 +4798,19 @@
         <v>9</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4817,19 +4818,19 @@
         <v>9</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -4837,16 +4838,16 @@
         <v>9</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>122</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>123</v>
@@ -4857,16 +4858,16 @@
         <v>9</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>124</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>125</v>
@@ -4877,10 +4878,10 @@
         <v>9</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>126</v>
@@ -4897,10 +4898,10 @@
         <v>9</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>128</v>
@@ -4917,39 +4918,39 @@
         <v>9</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D65" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D66" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E66" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="F66" s="9" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B66" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -4957,19 +4958,19 @@
         <v>9</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -4977,19 +4978,19 @@
         <v>9</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4997,16 +4998,16 @@
         <v>9</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>136</v>
@@ -5017,10 +5018,10 @@
         <v>9</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>137</v>
@@ -5037,10 +5038,10 @@
         <v>9</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>139</v>
@@ -5057,10 +5058,10 @@
         <v>9</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>141</v>
@@ -5077,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>143</v>
@@ -5097,10 +5098,10 @@
         <v>9</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>145</v>
@@ -5117,10 +5118,10 @@
         <v>9</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>147</v>
@@ -5137,10 +5138,10 @@
         <v>9</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>149</v>
@@ -5157,10 +5158,10 @@
         <v>9</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>151</v>
@@ -5177,10 +5178,10 @@
         <v>9</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>153</v>
@@ -5197,19 +5198,19 @@
         <v>9</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -5217,39 +5218,39 @@
         <v>9</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>27</v>
       </c>
       <c r="F80" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F81" s="11" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -5257,19 +5258,19 @@
         <v>9</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>158</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -5277,16 +5278,16 @@
         <v>9</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>159</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>160</v>
@@ -5297,10 +5298,10 @@
         <v>9</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>161</v>
@@ -5317,16 +5318,16 @@
         <v>9</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>163</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>164</v>
@@ -5337,16 +5338,16 @@
         <v>9</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>165</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>166</v>
@@ -5357,16 +5358,16 @@
         <v>9</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>167</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>168</v>
@@ -5377,39 +5378,39 @@
         <v>9</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>27</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="C89" s="9" t="s">
+      <c r="A89" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F89" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -5417,19 +5418,19 @@
         <v>9</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>172</v>
+        <v>12</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>173</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -5437,16 +5438,16 @@
         <v>9</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>174</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>175</v>
@@ -5457,19 +5458,19 @@
         <v>9</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -5477,19 +5478,19 @@
         <v>9</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -5497,19 +5498,19 @@
         <v>9</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -5517,16 +5518,16 @@
         <v>9</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>179</v>
+        <v>50</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>180</v>
@@ -5537,10 +5538,10 @@
         <v>9</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>181</v>
@@ -5557,10 +5558,10 @@
         <v>9</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>183</v>
@@ -5577,16 +5578,16 @@
         <v>9</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>185</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>186</v>
@@ -5597,39 +5598,39 @@
         <v>9</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D99" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D100" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E99" s="8" t="s">
+      <c r="E100" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F99" s="9" t="s">
+      <c r="F100" s="9" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B100" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="D100" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F100" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -5637,19 +5638,19 @@
         <v>9</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>190</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -5657,10 +5658,10 @@
         <v>9</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>191</v>
@@ -5677,16 +5678,16 @@
         <v>9</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>193</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F103" s="11" t="s">
         <v>194</v>
@@ -5697,16 +5698,16 @@
         <v>9</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>195</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F104" s="11" t="s">
         <v>196</v>
@@ -5717,19 +5718,19 @@
         <v>9</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -5737,16 +5738,16 @@
         <v>9</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>198</v>
+        <v>89</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F106" s="11" t="s">
         <v>199</v>
@@ -5757,10 +5758,10 @@
         <v>9</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>200</v>
@@ -5777,10 +5778,10 @@
         <v>9</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>202</v>
@@ -5797,10 +5798,10 @@
         <v>9</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>204</v>
@@ -5817,19 +5818,19 @@
         <v>9</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>141</v>
+        <v>206</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>22</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -5837,13 +5838,13 @@
         <v>9</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>207</v>
+        <v>143</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>22</v>
@@ -5857,39 +5858,39 @@
         <v>9</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D112" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F112" s="11" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D113" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E112" s="10" t="s">
+      <c r="E113" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F112" s="11" t="s">
+      <c r="F113" s="11" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D113" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E113" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -5897,19 +5898,19 @@
         <v>9</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>211</v>
+        <v>12</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>212</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -5917,10 +5918,10 @@
         <v>9</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>213</v>
@@ -5937,10 +5938,10 @@
         <v>9</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>215</v>
@@ -5957,16 +5958,16 @@
         <v>9</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>217</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>218</v>
@@ -5977,39 +5978,39 @@
         <v>9</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>219</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B119" s="8" t="s">
+      <c r="A119" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D119" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C119" s="9" t="s">
+      <c r="E119" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119" s="7" t="s">
         <v>222</v>
-      </c>
-      <c r="D119" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F119" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -6017,19 +6018,19 @@
         <v>9</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>223</v>
+        <v>12</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F120" s="9" t="s">
-        <v>224</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -6037,10 +6038,10 @@
         <v>9</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D121" s="8" t="s">
         <v>225</v>
@@ -6057,19 +6058,19 @@
         <v>9</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>50</v>
+        <v>227</v>
       </c>
       <c r="E122" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F122" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -6077,39 +6078,39 @@
         <v>9</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D123" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D124" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E123" s="8" t="s">
+      <c r="E124" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F123" s="9" t="s">
+      <c r="F124" s="9" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B124" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F124" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -6117,19 +6118,19 @@
         <v>9</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>230</v>
+        <v>12</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>231</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -6137,16 +6138,16 @@
         <v>9</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D126" s="10" t="s">
         <v>232</v>
       </c>
       <c r="E126" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F126" s="11" t="s">
         <v>233</v>
@@ -6157,10 +6158,10 @@
         <v>9</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>234</v>
@@ -6177,16 +6178,16 @@
         <v>9</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>236</v>
       </c>
       <c r="E128" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F128" s="11" t="s">
         <v>237</v>
@@ -6197,16 +6198,16 @@
         <v>9</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D129" s="10" t="s">
         <v>238</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F129" s="11" t="s">
         <v>239</v>
@@ -6217,16 +6218,16 @@
         <v>9</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>240</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F130" s="11" t="s">
         <v>241</v>
@@ -6237,16 +6238,16 @@
         <v>9</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D131" s="10" t="s">
         <v>242</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>243</v>
@@ -6257,19 +6258,19 @@
         <v>9</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>50</v>
+        <v>244</v>
       </c>
       <c r="E132" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -6277,39 +6278,39 @@
         <v>9</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D133" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E133" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F133" s="11" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D134" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E133" s="10" t="s">
+      <c r="E134" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F133" s="11" t="s">
+      <c r="F134" s="11" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -6317,19 +6318,19 @@
         <v>9</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>230</v>
+        <v>12</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>231</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -6337,19 +6338,19 @@
         <v>9</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>65</v>
+        <v>232</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>158</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -6357,19 +6358,19 @@
         <v>9</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>247</v>
+        <v>65</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="F137" s="6" t="s">
-        <v>249</v>
+        <v>13</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -6377,16 +6378,16 @@
         <v>9</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D138" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E138" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>251</v>
@@ -6397,16 +6398,16 @@
         <v>9</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>252</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>253</v>
@@ -6417,39 +6418,39 @@
         <v>9</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D140" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D141" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E140" s="6" t="s">
+      <c r="E141" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F140" s="7" t="s">
+      <c r="F141" s="7" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="C141" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="D141" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E141" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F141" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6457,19 +6458,19 @@
         <v>9</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>256</v>
+        <v>12</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F142" s="9" t="s">
-        <v>257</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -6477,19 +6478,19 @@
         <v>9</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>50</v>
+        <v>258</v>
       </c>
       <c r="E143" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F143" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6497,13 +6498,13 @@
         <v>9</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="E144" s="8" t="s">
         <v>16</v>
@@ -6517,19 +6518,19 @@
         <v>9</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>31</v>
+        <v>261</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F145" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -6537,39 +6538,39 @@
         <v>9</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E146" s="8" t="s">
         <v>27</v>
       </c>
       <c r="F146" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F147" s="9" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B147" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="C147" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="D147" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F147" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -6577,19 +6578,19 @@
         <v>9</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D148" s="10" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>264</v>
+        <v>14</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -6597,16 +6598,16 @@
         <v>9</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>265</v>
+        <v>38</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F149" s="11" t="s">
         <v>266</v>
@@ -6617,19 +6618,19 @@
         <v>9</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>65</v>
+        <v>267</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F150" s="11" t="s">
-        <v>158</v>
+        <v>268</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -6637,19 +6638,19 @@
         <v>9</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>267</v>
+        <v>65</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F151" s="11" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -6657,16 +6658,16 @@
         <v>9</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D152" s="10" t="s">
         <v>269</v>
       </c>
       <c r="E152" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F152" s="11" t="s">
         <v>270</v>
@@ -6677,16 +6678,16 @@
         <v>9</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D153" s="10" t="s">
         <v>271</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F153" s="11" t="s">
         <v>272</v>
@@ -6697,39 +6698,39 @@
         <v>9</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D154" s="10" t="s">
         <v>273</v>
       </c>
       <c r="E154" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F154" s="11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="D155" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E155" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F154" s="11" t="s">
+      <c r="F155" s="11" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="C155" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="D155" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F155" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -6737,19 +6738,19 @@
         <v>9</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>276</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -6757,16 +6758,16 @@
         <v>9</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>277</v>
+        <v>191</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F157" s="7" t="s">
         <v>278</v>
@@ -6777,10 +6778,10 @@
         <v>9</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>279</v>
@@ -6797,16 +6798,16 @@
         <v>9</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>281</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F159" s="7" t="s">
         <v>282</v>
@@ -6817,16 +6818,16 @@
         <v>9</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>283</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F160" s="7" t="s">
         <v>284</v>
@@ -6837,16 +6838,16 @@
         <v>9</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>285</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F161" s="7" t="s">
         <v>286</v>
@@ -6857,16 +6858,16 @@
         <v>9</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>287</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F162" s="7" t="s">
         <v>288</v>
@@ -6877,10 +6878,10 @@
         <v>9</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>289</v>
@@ -6897,16 +6898,16 @@
         <v>9</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>291</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F164" s="7" t="s">
         <v>292</v>
@@ -6917,10 +6918,10 @@
         <v>9</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>293</v>
@@ -6937,19 +6938,19 @@
         <v>9</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>185</v>
+        <v>295</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>186</v>
+        <v>296</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -6957,19 +6958,19 @@
         <v>9</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>295</v>
+        <v>187</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>296</v>
+        <v>188</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -6977,10 +6978,10 @@
         <v>9</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>297</v>
@@ -6993,23 +6994,23 @@
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="A169" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B169" s="8" t="s">
+      <c r="A169" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D169" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="C169" s="9" t="s">
+      <c r="E169" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F169" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="D169" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E169" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F169" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -7017,19 +7018,19 @@
         <v>9</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>265</v>
+        <v>12</v>
       </c>
       <c r="E170" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F170" s="9" t="s">
-        <v>301</v>
+        <v>14</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -7037,13 +7038,13 @@
         <v>9</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="E171" s="8" t="s">
         <v>13</v>
@@ -7057,19 +7058,19 @@
         <v>9</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>191</v>
+        <v>304</v>
       </c>
       <c r="E172" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F172" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -7077,13 +7078,13 @@
         <v>9</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>305</v>
+        <v>193</v>
       </c>
       <c r="E173" s="8" t="s">
         <v>13</v>
@@ -7097,10 +7098,10 @@
         <v>9</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D174" s="8" t="s">
         <v>307</v>
@@ -7117,16 +7118,16 @@
         <v>9</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D175" s="8" t="s">
         <v>309</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>310</v>
@@ -7137,16 +7138,16 @@
         <v>9</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D176" s="8" t="s">
         <v>311</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>312</v>
@@ -7157,10 +7158,10 @@
         <v>9</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C177" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D177" s="8" t="s">
         <v>313</v>
@@ -7177,10 +7178,10 @@
         <v>9</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D178" s="8" t="s">
         <v>315</v>
@@ -7197,10 +7198,10 @@
         <v>9</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D179" s="8" t="s">
         <v>317</v>
@@ -7217,10 +7218,10 @@
         <v>9</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D180" s="8" t="s">
         <v>319</v>
@@ -7237,19 +7238,19 @@
         <v>9</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F181" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -7257,10 +7258,10 @@
         <v>9</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C182" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D182" s="8" t="s">
         <v>297</v>
@@ -7269,7 +7270,7 @@
         <v>27</v>
       </c>
       <c r="F182" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -7277,39 +7278,39 @@
         <v>9</v>
       </c>
       <c r="B183" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C183" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="D183" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="C183" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="D183" s="8" t="s">
-        <v>323</v>
-      </c>
       <c r="E183" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F183" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="F183" s="9" t="s">
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C184" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="D184" s="8" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="184" spans="1:6">
-      <c r="A184" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B184" s="10" t="s">
+      <c r="E184" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="C184" s="11" t="s">
+      <c r="F184" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="D184" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E184" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F184" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -7317,19 +7318,19 @@
         <v>9</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D185" s="10" t="s">
-        <v>328</v>
+        <v>12</v>
       </c>
       <c r="E185" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F185" s="11" t="s">
-        <v>329</v>
+        <v>14</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -7337,10 +7338,10 @@
         <v>9</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D186" s="10" t="s">
         <v>330</v>
@@ -7357,16 +7358,16 @@
         <v>9</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D187" s="10" t="s">
         <v>332</v>
       </c>
       <c r="E187" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F187" s="11" t="s">
         <v>333</v>
@@ -7377,16 +7378,16 @@
         <v>9</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D188" s="10" t="s">
         <v>334</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F188" s="11" t="s">
         <v>335</v>
@@ -7397,10 +7398,10 @@
         <v>9</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D189" s="10" t="s">
         <v>336</v>
@@ -7417,16 +7418,16 @@
         <v>9</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D190" s="10" t="s">
         <v>338</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F190" s="11" t="s">
         <v>339</v>
@@ -7437,16 +7438,16 @@
         <v>9</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D191" s="10" t="s">
         <v>340</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="F191" s="11" t="s">
         <v>341</v>
@@ -7457,39 +7458,39 @@
         <v>9</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D192" s="10" t="s">
         <v>342</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F192" s="11" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="193" spans="1:6">
-      <c r="A193" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B193" s="6" t="s">
+      <c r="A193" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C193" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="D193" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="C193" s="7" t="s">
+      <c r="E193" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F193" s="11" t="s">
         <v>345</v>
-      </c>
-      <c r="D193" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E193" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F193" s="7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -7497,19 +7498,19 @@
         <v>9</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>346</v>
+        <v>12</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>347</v>
+        <v>35</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -7517,16 +7518,16 @@
         <v>9</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D195" s="6" t="s">
         <v>348</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F195" s="7" t="s">
         <v>349</v>
@@ -7537,19 +7538,19 @@
         <v>9</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>265</v>
+        <v>350</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -7557,10 +7558,10 @@
         <v>9</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D197" s="6" t="s">
         <v>267</v>
@@ -7569,7 +7570,7 @@
         <v>13</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -7577,19 +7578,19 @@
         <v>9</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>65</v>
+        <v>269</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -7597,16 +7598,16 @@
         <v>9</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="E199" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F199" s="7" t="s">
         <v>354</v>
@@ -7617,16 +7618,16 @@
         <v>9</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D200" s="6" t="s">
         <v>355</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F200" s="7" t="s">
         <v>356</v>
@@ -7637,10 +7638,10 @@
         <v>9</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D201" s="6" t="s">
         <v>357</v>
@@ -7657,10 +7658,10 @@
         <v>9</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D202" s="6" t="s">
         <v>359</v>
@@ -7677,16 +7678,16 @@
         <v>9</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D203" s="6" t="s">
         <v>361</v>
       </c>
       <c r="E203" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F203" s="7" t="s">
         <v>362</v>
@@ -7697,19 +7698,39 @@
         <v>9</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>363</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F204" s="7" t="s">
         <v>364</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D205" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E205" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/数据库表结构.xlsx
+++ b/数据库表结构.xlsx
@@ -682,6 +682,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>状态（使用中</t>
     </r>
     <r>
@@ -1568,18 +1573,13 @@
     <t>更新时间</t>
   </si>
   <si>
-    <t>STEP_LOG</t>
+    <t>EXECUTION_LOG</t>
   </si>
   <si>
     <t>执行日志表</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>日志来源（任务</t>
     </r>
     <r>
@@ -1796,13 +1796,46 @@
     <t>current_node_id_ref</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>当前执行节点在流程模型内的</t>
+    <t>当前主流程执行到的节点ID</t>
+  </si>
+  <si>
+    <t>resource_map</t>
+  </si>
+  <si>
+    <t>资源绑定列表（实例化）</t>
+  </si>
+  <si>
+    <t>task_variables</t>
+  </si>
+  <si>
+    <t>全局共享变量</t>
+  </si>
+  <si>
+    <t>start_time</t>
+  </si>
+  <si>
+    <t>任务开始时间</t>
+  </si>
+  <si>
+    <t>end_time</t>
+  </si>
+  <si>
+    <t>任务结束时间（空表示未结束）</t>
+  </si>
+  <si>
+    <t>TASK_STEP</t>
+  </si>
+  <si>
+    <t>任务过程表</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>所属任务</t>
     </r>
     <r>
       <rPr>
@@ -1812,53 +1845,18 @@
       </rPr>
       <t>ID</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（只记录主流程）</t>
-    </r>
-  </si>
-  <si>
-    <t>resource_map</t>
-  </si>
-  <si>
-    <t>资源绑定列表（实例化）</t>
-  </si>
-  <si>
-    <t>task_variables</t>
-  </si>
-  <si>
-    <t>全局共享变量</t>
-  </si>
-  <si>
-    <t>start_time</t>
-  </si>
-  <si>
-    <t>任务开始时间</t>
-  </si>
-  <si>
-    <t>end_time</t>
-  </si>
-  <si>
-    <t>任务结束时间（空表示未结束）</t>
-  </si>
-  <si>
-    <t>TASK_STEP</t>
-  </si>
-  <si>
-    <t>任务过程表</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>所属任务</t>
+  </si>
+  <si>
+    <t>flow_node_id</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>执行的节点在节点表中的</t>
     </r>
     <r>
       <rPr>
@@ -1870,16 +1868,19 @@
     </r>
   </si>
   <si>
-    <t>flow_node_id</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>执行的节点在节点表中的</t>
+    <t>执行的节点在流程内ID（相对ID）</t>
+  </si>
+  <si>
+    <t>parent_step_id</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>父节点</t>
     </r>
     <r>
       <rPr>
@@ -1889,15 +1890,13 @@
       </rPr>
       <t>ID</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>执行的节点在自己流程内的</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（主流程为</t>
     </r>
     <r>
       <rPr>
@@ -1905,67 +1904,6 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（相对</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <t>parent_step_id</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>父节点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（主流程为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve"> NULL</t>
     </r>
     <r>
@@ -1974,7 +1912,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>，子流程中的节点指向父节点的节点表</t>
+      <t>，子流程中的节点指向父节点的过程表</t>
     </r>
     <r>
       <rPr>
@@ -3635,7 +3573,7 @@
     <col min="3" max="3" width="17.8888888888889" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.1111111111111" style="1" customWidth="1"/>
     <col min="5" max="5" width="26.2222222222222" style="1" customWidth="1"/>
-    <col min="6" max="6" width="56.6666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="73" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/数据库表结构.xlsx
+++ b/数据库表结构.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="369">
   <si>
     <t>数据库名：lab</t>
   </si>
@@ -823,6 +823,12 @@
     <t>绑定的设备点</t>
   </si>
   <si>
+    <t>lifecycle_status</t>
+  </si>
+  <si>
+    <t>设备实例生命状态（使用中/已废弃）</t>
+  </si>
+  <si>
     <t>picture</t>
   </si>
   <si>
@@ -1580,6 +1586,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>日志来源（任务</t>
     </r>
     <r>
@@ -3565,7 +3576,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -4882,33 +4893,33 @@
         <v>121</v>
       </c>
       <c r="D66" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D67" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E67" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="F67" s="9" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -4916,19 +4927,19 @@
         <v>9</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>135</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4936,19 +4947,19 @@
         <v>9</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4956,16 +4967,16 @@
         <v>9</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>138</v>
@@ -4976,10 +4987,10 @@
         <v>9</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>139</v>
@@ -4996,10 +5007,10 @@
         <v>9</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>141</v>
@@ -5016,10 +5027,10 @@
         <v>9</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>143</v>
@@ -5036,10 +5047,10 @@
         <v>9</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>145</v>
@@ -5056,10 +5067,10 @@
         <v>9</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>147</v>
@@ -5076,10 +5087,10 @@
         <v>9</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>149</v>
@@ -5096,10 +5107,10 @@
         <v>9</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>151</v>
@@ -5116,10 +5127,10 @@
         <v>9</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>153</v>
@@ -5136,10 +5147,10 @@
         <v>9</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>155</v>
@@ -5156,19 +5167,19 @@
         <v>9</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>29</v>
+        <v>157</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -5176,39 +5187,39 @@
         <v>9</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>27</v>
       </c>
       <c r="F81" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F82" s="11" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -5216,19 +5227,19 @@
         <v>9</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>160</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -5236,16 +5247,16 @@
         <v>9</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>161</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>162</v>
@@ -5256,16 +5267,16 @@
         <v>9</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>163</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>164</v>
@@ -5276,16 +5287,16 @@
         <v>9</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>165</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>166</v>
@@ -5296,16 +5307,16 @@
         <v>9</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>167</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>168</v>
@@ -5316,16 +5327,16 @@
         <v>9</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>169</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>170</v>
@@ -5336,39 +5347,39 @@
         <v>9</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>31</v>
+        <v>171</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>27</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C90" s="9" t="s">
+      <c r="A90" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F90" s="7" t="s">
         <v>173</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -5376,19 +5387,19 @@
         <v>9</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>174</v>
+        <v>12</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>175</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -5396,16 +5407,16 @@
         <v>9</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>176</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>177</v>
@@ -5416,19 +5427,19 @@
         <v>9</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -5436,19 +5447,19 @@
         <v>9</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -5456,19 +5467,19 @@
         <v>9</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -5476,16 +5487,16 @@
         <v>9</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>182</v>
@@ -5496,10 +5507,10 @@
         <v>9</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>183</v>
@@ -5516,10 +5527,10 @@
         <v>9</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>185</v>
@@ -5536,16 +5547,16 @@
         <v>9</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>187</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>188</v>
@@ -5556,39 +5567,39 @@
         <v>9</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D100" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D101" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E100" s="8" t="s">
+      <c r="E101" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F100" s="9" t="s">
+      <c r="F101" s="9" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B101" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="D101" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F101" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -5596,19 +5607,19 @@
         <v>9</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>191</v>
+        <v>12</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>192</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -5616,10 +5627,10 @@
         <v>9</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>193</v>
@@ -5636,16 +5647,16 @@
         <v>9</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>195</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F104" s="11" t="s">
         <v>196</v>
@@ -5656,16 +5667,16 @@
         <v>9</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>197</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F105" s="11" t="s">
         <v>198</v>
@@ -5676,19 +5687,19 @@
         <v>9</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -5696,16 +5707,16 @@
         <v>9</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>200</v>
+        <v>89</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>201</v>
@@ -5716,10 +5727,10 @@
         <v>9</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>202</v>
@@ -5736,10 +5747,10 @@
         <v>9</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>204</v>
@@ -5756,10 +5767,10 @@
         <v>9</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>206</v>
@@ -5776,19 +5787,19 @@
         <v>9</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>22</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -5796,13 +5807,13 @@
         <v>9</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>209</v>
+        <v>145</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>22</v>
@@ -5816,39 +5827,39 @@
         <v>9</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D113" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F113" s="11" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D114" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E113" s="10" t="s">
+      <c r="E114" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F113" s="11" t="s">
+      <c r="F114" s="11" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -5856,19 +5867,19 @@
         <v>9</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>213</v>
+        <v>12</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -5876,10 +5887,10 @@
         <v>9</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>215</v>
@@ -5896,10 +5907,10 @@
         <v>9</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>217</v>
@@ -5916,16 +5927,16 @@
         <v>9</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>219</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>220</v>
@@ -5936,39 +5947,39 @@
         <v>9</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>221</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B120" s="8" t="s">
+      <c r="A120" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D120" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="C120" s="9" t="s">
+      <c r="E120" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F120" s="7" t="s">
         <v>224</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F120" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -5976,19 +5987,19 @@
         <v>9</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>225</v>
+        <v>12</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F121" s="9" t="s">
-        <v>226</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -5996,10 +6007,10 @@
         <v>9</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D122" s="8" t="s">
         <v>227</v>
@@ -6016,19 +6027,19 @@
         <v>9</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>50</v>
+        <v>229</v>
       </c>
       <c r="E123" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F123" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -6036,39 +6047,39 @@
         <v>9</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D124" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D125" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E124" s="8" t="s">
+      <c r="E125" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F124" s="9" t="s">
+      <c r="F125" s="9" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B125" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="C125" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F125" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -6076,19 +6087,19 @@
         <v>9</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>232</v>
+        <v>12</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>233</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -6096,16 +6107,16 @@
         <v>9</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D127" s="10" t="s">
         <v>234</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F127" s="11" t="s">
         <v>235</v>
@@ -6116,10 +6127,10 @@
         <v>9</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D128" s="10" t="s">
         <v>236</v>
@@ -6136,16 +6147,16 @@
         <v>9</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D129" s="10" t="s">
         <v>238</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F129" s="11" t="s">
         <v>239</v>
@@ -6156,16 +6167,16 @@
         <v>9</v>
       </c>
       <c r="B130" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D130" s="10" t="s">
         <v>240</v>
       </c>
       <c r="E130" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F130" s="11" t="s">
         <v>241</v>
@@ -6176,16 +6187,16 @@
         <v>9</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D131" s="10" t="s">
         <v>242</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>243</v>
@@ -6196,16 +6207,16 @@
         <v>9</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D132" s="10" t="s">
         <v>244</v>
       </c>
       <c r="E132" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>245</v>
@@ -6216,19 +6227,19 @@
         <v>9</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D133" s="10" t="s">
-        <v>50</v>
+        <v>246</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>16</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -6236,39 +6247,39 @@
         <v>9</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D134" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134" s="11" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C135" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D135" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E134" s="10" t="s">
+      <c r="E135" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F134" s="11" t="s">
+      <c r="F135" s="11" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D135" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E135" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F135" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -6276,19 +6287,19 @@
         <v>9</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>232</v>
+        <v>12</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>233</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -6296,19 +6307,19 @@
         <v>9</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>65</v>
+        <v>234</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>160</v>
+        <v>235</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -6316,19 +6327,19 @@
         <v>9</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>249</v>
+        <v>65</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>251</v>
+        <v>13</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -6336,16 +6347,16 @@
         <v>9</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D139" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="E139" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="E139" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>253</v>
@@ -6356,16 +6367,16 @@
         <v>9</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>254</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>255</v>
@@ -6376,39 +6387,39 @@
         <v>9</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D141" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D142" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E141" s="6" t="s">
+      <c r="E142" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F141" s="7" t="s">
+      <c r="F142" s="7" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B142" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="C142" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="D142" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E142" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F142" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -6416,19 +6427,19 @@
         <v>9</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>258</v>
+        <v>12</v>
       </c>
       <c r="E143" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F143" s="9" t="s">
-        <v>259</v>
+        <v>14</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6436,19 +6447,19 @@
         <v>9</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="E144" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F144" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -6456,13 +6467,13 @@
         <v>9</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>261</v>
+        <v>50</v>
       </c>
       <c r="E145" s="8" t="s">
         <v>16</v>
@@ -6476,19 +6487,19 @@
         <v>9</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>31</v>
+        <v>263</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F146" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -6496,39 +6507,39 @@
         <v>9</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E147" s="8" t="s">
         <v>27</v>
       </c>
       <c r="F147" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C148" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F148" s="9" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B148" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="C148" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D148" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E148" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F148" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -6536,19 +6547,19 @@
         <v>9</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D149" s="10" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F149" s="11" t="s">
-        <v>266</v>
+        <v>14</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -6556,16 +6567,16 @@
         <v>9</v>
       </c>
       <c r="B150" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D150" s="10" t="s">
-        <v>267</v>
+        <v>38</v>
       </c>
       <c r="E150" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F150" s="11" t="s">
         <v>268</v>
@@ -6576,19 +6587,19 @@
         <v>9</v>
       </c>
       <c r="B151" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D151" s="10" t="s">
-        <v>65</v>
+        <v>269</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F151" s="11" t="s">
-        <v>160</v>
+        <v>270</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -6596,19 +6607,19 @@
         <v>9</v>
       </c>
       <c r="B152" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D152" s="10" t="s">
-        <v>269</v>
+        <v>65</v>
       </c>
       <c r="E152" s="10" t="s">
         <v>13</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>270</v>
+        <v>162</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -6616,16 +6627,16 @@
         <v>9</v>
       </c>
       <c r="B153" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D153" s="10" t="s">
         <v>271</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F153" s="11" t="s">
         <v>272</v>
@@ -6636,16 +6647,16 @@
         <v>9</v>
       </c>
       <c r="B154" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D154" s="10" t="s">
         <v>273</v>
       </c>
       <c r="E154" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F154" s="11" t="s">
         <v>274</v>
@@ -6656,39 +6667,39 @@
         <v>9</v>
       </c>
       <c r="B155" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D155" s="10" t="s">
         <v>275</v>
       </c>
       <c r="E155" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F155" s="11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C156" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D156" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="E156" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F155" s="11" t="s">
+      <c r="F156" s="11" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F156" s="7" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -6696,19 +6707,19 @@
         <v>9</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>191</v>
+        <v>12</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -6716,16 +6727,16 @@
         <v>9</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>279</v>
+        <v>193</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F158" s="7" t="s">
         <v>280</v>
@@ -6736,10 +6747,10 @@
         <v>9</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>281</v>
@@ -6756,16 +6767,16 @@
         <v>9</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>283</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F160" s="7" t="s">
         <v>284</v>
@@ -6776,16 +6787,16 @@
         <v>9</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>285</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F161" s="7" t="s">
         <v>286</v>
@@ -6796,16 +6807,16 @@
         <v>9</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>287</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F162" s="7" t="s">
         <v>288</v>
@@ -6816,16 +6827,16 @@
         <v>9</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>289</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F163" s="7" t="s">
         <v>290</v>
@@ -6836,10 +6847,10 @@
         <v>9</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>291</v>
@@ -6856,16 +6867,16 @@
         <v>9</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>293</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F165" s="7" t="s">
         <v>294</v>
@@ -6876,10 +6887,10 @@
         <v>9</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>295</v>
@@ -6896,19 +6907,19 @@
         <v>9</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>187</v>
+        <v>297</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>188</v>
+        <v>298</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -6916,19 +6927,19 @@
         <v>9</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>297</v>
+        <v>189</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>298</v>
+        <v>190</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -6936,10 +6947,10 @@
         <v>9</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>299</v>
@@ -6952,23 +6963,23 @@
       </c>
     </row>
     <row r="170" spans="1:6">
-      <c r="A170" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B170" s="8" t="s">
+      <c r="A170" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="D170" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="C170" s="9" t="s">
+      <c r="E170" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F170" s="7" t="s">
         <v>302</v>
-      </c>
-      <c r="D170" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E170" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F170" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -6976,19 +6987,19 @@
         <v>9</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>267</v>
+        <v>12</v>
       </c>
       <c r="E171" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F171" s="9" t="s">
-        <v>303</v>
+        <v>14</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -6996,13 +7007,13 @@
         <v>9</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="E172" s="8" t="s">
         <v>13</v>
@@ -7016,19 +7027,19 @@
         <v>9</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>193</v>
+        <v>306</v>
       </c>
       <c r="E173" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F173" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -7036,13 +7047,13 @@
         <v>9</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>307</v>
+        <v>195</v>
       </c>
       <c r="E174" s="8" t="s">
         <v>13</v>
@@ -7056,10 +7067,10 @@
         <v>9</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D175" s="8" t="s">
         <v>309</v>
@@ -7076,16 +7087,16 @@
         <v>9</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D176" s="8" t="s">
         <v>311</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>312</v>
@@ -7096,16 +7107,16 @@
         <v>9</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C177" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D177" s="8" t="s">
         <v>313</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>314</v>
@@ -7116,10 +7127,10 @@
         <v>9</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D178" s="8" t="s">
         <v>315</v>
@@ -7136,10 +7147,10 @@
         <v>9</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D179" s="8" t="s">
         <v>317</v>
@@ -7156,10 +7167,10 @@
         <v>9</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D180" s="8" t="s">
         <v>319</v>
@@ -7176,10 +7187,10 @@
         <v>9</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D181" s="8" t="s">
         <v>321</v>
@@ -7196,19 +7207,19 @@
         <v>9</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C182" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F182" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -7216,10 +7227,10 @@
         <v>9</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C183" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D183" s="8" t="s">
         <v>299</v>
@@ -7228,7 +7239,7 @@
         <v>27</v>
       </c>
       <c r="F183" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -7236,39 +7247,39 @@
         <v>9</v>
       </c>
       <c r="B184" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C184" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D184" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="C184" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="D184" s="8" t="s">
-        <v>325</v>
-      </c>
       <c r="E184" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F184" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="F184" s="9" t="s">
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C185" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D185" s="8" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="185" spans="1:6">
-      <c r="A185" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B185" s="10" t="s">
+      <c r="E185" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="C185" s="11" t="s">
+      <c r="F185" s="9" t="s">
         <v>329</v>
-      </c>
-      <c r="D185" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E185" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F185" s="11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -7276,19 +7287,19 @@
         <v>9</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D186" s="10" t="s">
-        <v>330</v>
+        <v>12</v>
       </c>
       <c r="E186" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F186" s="11" t="s">
-        <v>331</v>
+        <v>14</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -7296,10 +7307,10 @@
         <v>9</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D187" s="10" t="s">
         <v>332</v>
@@ -7316,16 +7327,16 @@
         <v>9</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C188" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D188" s="10" t="s">
         <v>334</v>
       </c>
       <c r="E188" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F188" s="11" t="s">
         <v>335</v>
@@ -7336,16 +7347,16 @@
         <v>9</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D189" s="10" t="s">
         <v>336</v>
       </c>
       <c r="E189" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F189" s="11" t="s">
         <v>337</v>
@@ -7356,10 +7367,10 @@
         <v>9</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D190" s="10" t="s">
         <v>338</v>
@@ -7376,16 +7387,16 @@
         <v>9</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D191" s="10" t="s">
         <v>340</v>
       </c>
       <c r="E191" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F191" s="11" t="s">
         <v>341</v>
@@ -7396,16 +7407,16 @@
         <v>9</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D192" s="10" t="s">
         <v>342</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="F192" s="11" t="s">
         <v>343</v>
@@ -7416,39 +7427,39 @@
         <v>9</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D193" s="10" t="s">
         <v>344</v>
       </c>
       <c r="E193" s="10" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F193" s="11" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="194" spans="1:6">
-      <c r="A194" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B194" s="6" t="s">
+      <c r="A194" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C194" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D194" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="C194" s="7" t="s">
+      <c r="E194" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F194" s="11" t="s">
         <v>347</v>
-      </c>
-      <c r="D194" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E194" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F194" s="7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -7456,19 +7467,19 @@
         <v>9</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>348</v>
+        <v>12</v>
       </c>
       <c r="E195" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>349</v>
+        <v>35</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -7476,16 +7487,16 @@
         <v>9</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D196" s="6" t="s">
         <v>350</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F196" s="7" t="s">
         <v>351</v>
@@ -7496,19 +7507,19 @@
         <v>9</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>267</v>
+        <v>352</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -7516,10 +7527,10 @@
         <v>9</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D198" s="6" t="s">
         <v>269</v>
@@ -7528,7 +7539,7 @@
         <v>13</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -7536,19 +7547,19 @@
         <v>9</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>65</v>
+        <v>271</v>
       </c>
       <c r="E199" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -7556,16 +7567,16 @@
         <v>9</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>355</v>
+        <v>65</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F200" s="7" t="s">
         <v>356</v>
@@ -7576,16 +7587,16 @@
         <v>9</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D201" s="6" t="s">
         <v>357</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F201" s="7" t="s">
         <v>358</v>
@@ -7596,10 +7607,10 @@
         <v>9</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D202" s="6" t="s">
         <v>359</v>
@@ -7616,10 +7627,10 @@
         <v>9</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D203" s="6" t="s">
         <v>361</v>
@@ -7636,16 +7647,16 @@
         <v>9</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>363</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F204" s="7" t="s">
         <v>364</v>
@@ -7656,19 +7667,39 @@
         <v>9</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>365</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F205" s="7" t="s">
         <v>366</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="D206" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/数据库表结构.xlsx
+++ b/数据库表结构.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SmartLab2.0\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
@@ -2261,65 +2266,19 @@
     <t>observed_variable</t>
   </si>
   <si>
-    <t>被观测的变量名</t>
-  </si>
-  <si>
-    <t>expected_condition</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>预期条件（如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> LT 200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+    <t>约束涉及的变量名</t>
+  </si>
+  <si>
+    <t>expression</t>
+  </si>
+  <si>
+    <t>约束表达式</t>
   </si>
   <si>
     <t>actual_value</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>实际值（如</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 215.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+    <t>实际值</t>
   </si>
   <si>
     <t>variable_snapshot</t>
@@ -7596,7 +7555,7 @@
         <v>357</v>
       </c>
       <c r="E201" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F201" s="7" t="s">
         <v>358</v>
